--- a/docs/namelist.xlsx
+++ b/docs/namelist.xlsx
@@ -1,24 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\family-ledger_RevB\Lunch_HP\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B28A74-E2EC-45F5-99E0-402E53CBD467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2C41338-62DC-4033-B5ED-83CE0072E395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8DE58E48-9B51-414C-ABE7-C19446391599}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -27,139 +41,139 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
+    <t>Teo Kian Chai</t>
+  </si>
+  <si>
+    <t>Huang Tao</t>
+  </si>
+  <si>
+    <t>Alvin</t>
+  </si>
+  <si>
+    <t>Alberto</t>
+  </si>
+  <si>
+    <t>Roger</t>
+  </si>
+  <si>
+    <t>Victor Serra</t>
+  </si>
+  <si>
+    <t>Claudia Peiró</t>
+  </si>
+  <si>
+    <t>Ignacio Alejandre,</t>
+  </si>
+  <si>
+    <t>Miquel Riera,</t>
+  </si>
+  <si>
+    <t>Guille Erraez,</t>
+  </si>
+  <si>
+    <t>Gabriel Nogales</t>
+  </si>
+  <si>
+    <t>Raquel Wamp</t>
+  </si>
+  <si>
+    <t>Juan Esteban Rangel</t>
+  </si>
+  <si>
+    <t>Chuah, Nee Heng</t>
+  </si>
+  <si>
+    <t>Miquel Riera</t>
+  </si>
+  <si>
+    <t>Sheila Cabello</t>
+  </si>
+  <si>
+    <t>Pau Serra</t>
+  </si>
+  <si>
+    <t>Li Peng zhen</t>
+  </si>
+  <si>
+    <t>ALEJANDRO ALARCON CANO</t>
+  </si>
+  <si>
+    <t>JORDI MUNCUNILL FARRES</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Javier Velazquez</t>
+  </si>
+  <si>
+    <t>Tua, Marta</t>
+  </si>
+  <si>
+    <t>Tang, hong</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Zhou Yong</t>
+  </si>
+  <si>
+    <t>Zhou, HongLiang</t>
+  </si>
+  <si>
+    <t>Zhang, Xin-Guo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zhang, Hai-Tao </t>
+  </si>
+  <si>
+    <t>Zeng, Daniel</t>
+  </si>
+  <si>
+    <t>Yan, Hong-Ming</t>
+  </si>
+  <si>
+    <t>Xu, Jian</t>
+  </si>
+  <si>
+    <t>Xiong, Wenjun</t>
+  </si>
+  <si>
+    <t>Wang, Cheng-Yu</t>
+  </si>
+  <si>
+    <t>Wan, Jia-Nian</t>
+  </si>
+  <si>
+    <t>Su, Jun</t>
+  </si>
+  <si>
+    <t>Shi, Zhao-Yong</t>
+  </si>
+  <si>
+    <t>Qiao, Xiu-Jun</t>
+  </si>
+  <si>
+    <t>Mao, Kun</t>
+  </si>
+  <si>
+    <t>Liu, Jianping</t>
+  </si>
+  <si>
+    <t>Hu, Yao-Qing</t>
+  </si>
+  <si>
+    <t>Guo, Xiao-Jian</t>
+  </si>
+  <si>
+    <t>Ge, Neal</t>
+  </si>
+  <si>
+    <t>Dou, Cindy</t>
+  </si>
+  <si>
     <t>Name List</t>
-  </si>
-  <si>
-    <t>Dou, Cindy</t>
-  </si>
-  <si>
-    <t>Ge, Neal</t>
-  </si>
-  <si>
-    <t>Guo, Xiao-Jian</t>
-  </si>
-  <si>
-    <t>Hu, Yao-Qing</t>
-  </si>
-  <si>
-    <t>Liu, Jianping</t>
-  </si>
-  <si>
-    <t>Mao, Kun</t>
-  </si>
-  <si>
-    <t>Qiao, Xiu-Jun</t>
-  </si>
-  <si>
-    <t>Shi, Zhao-Yong</t>
-  </si>
-  <si>
-    <t>Su, Jun</t>
-  </si>
-  <si>
-    <t>Wan, Jia-Nian</t>
-  </si>
-  <si>
-    <t>Wang, Cheng-Yu</t>
-  </si>
-  <si>
-    <t>Xiong, Wenjun</t>
-  </si>
-  <si>
-    <t>Xu, Jian</t>
-  </si>
-  <si>
-    <t>Yan, Hong-Ming</t>
-  </si>
-  <si>
-    <t>Zeng, Daniel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhang, Hai-Tao </t>
-  </si>
-  <si>
-    <t>Zhang, Xin-Guo</t>
-  </si>
-  <si>
-    <t>Zhou, HongLiang</t>
-  </si>
-  <si>
-    <t>Zhou Yong</t>
-  </si>
-  <si>
-    <t>Alex</t>
-  </si>
-  <si>
-    <t>Tang, hong</t>
-  </si>
-  <si>
-    <t>Tua, Marta</t>
-  </si>
-  <si>
-    <t>Javier Velazquez</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>JORDI MUNCUNILL FARRES</t>
-  </si>
-  <si>
-    <t>ALEJANDRO ALARCON CANO</t>
-  </si>
-  <si>
-    <t>Li Peng zhen</t>
-  </si>
-  <si>
-    <t>Pau Serra</t>
-  </si>
-  <si>
-    <t>Sheila Cabello</t>
-  </si>
-  <si>
-    <t>Miquel Riera</t>
-  </si>
-  <si>
-    <t>Chuah, Nee Heng</t>
-  </si>
-  <si>
-    <t>Juan Esteban Rangel</t>
-  </si>
-  <si>
-    <t>Raquel Wamp</t>
-  </si>
-  <si>
-    <t>Gabriel Nogales</t>
-  </si>
-  <si>
-    <t>Guille Erraez,</t>
-  </si>
-  <si>
-    <t>Miquel Riera,</t>
-  </si>
-  <si>
-    <t>Ignacio Alejandre,</t>
-  </si>
-  <si>
-    <t>Claudia Peiró</t>
-  </si>
-  <si>
-    <t>Victor Serra</t>
-  </si>
-  <si>
-    <t>Roger</t>
-  </si>
-  <si>
-    <t>Alberto</t>
-  </si>
-  <si>
-    <t>Alvin</t>
-  </si>
-  <si>
-    <t>Huang Tao</t>
-  </si>
-  <si>
-    <t>Teo Kian Chai</t>
   </si>
 </sst>
 </file>
@@ -476,121 +490,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F40BBD-3BB5-473B-8B29-663679E89FCD}">
   <dimension ref="A1:A45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="24.7265625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
@@ -600,112 +611,112 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
